--- a/exports/ATHERENERG_full_report.xlsx
+++ b/exports/ATHERENERG_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:U14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>16.59</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>45965.38541666666</v>
+        <v>45965.55208333334</v>
       </c>
       <c r="H2" t="n">
-        <v>693.5</v>
+        <v>669</v>
       </c>
       <c r="I2" t="n">
         <v>670.5113999403475</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>175</v>
+        <v>175.1666666666667</v>
       </c>
       <c r="K2" t="n">
-        <v>127.83</v>
+        <v>119.78</v>
       </c>
       <c r="L2" t="n">
         <v>2.04</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>242</v>
+        <v>243</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>7</v>
+      </c>
+      <c r="U2" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>12.24</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>45989.38541666666</v>
+        <v>45989.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>704.25</v>
+        <v>715</v>
       </c>
       <c r="I3" t="n">
         <v>712.8671995037691</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>23.83333333333333</v>
+        <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>-5.27</v>
+        <v>-6.88</v>
       </c>
       <c r="L3" t="n">
-        <v>7.32</v>
+        <v>7.92</v>
       </c>
       <c r="M3" t="n">
         <v>2.56</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>8.69</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>45999.55208333334</v>
+        <v>46000.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>674.9</v>
+        <v>650.65</v>
       </c>
       <c r="I4" t="n">
         <v>657.3761385750178</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>-5.61</v>
+        <v>-9</v>
       </c>
       <c r="L4" t="n">
-        <v>8.42</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="M4" t="n">
         <v>0.25</v>
       </c>
       <c r="N4" t="n">
-        <v>2.98</v>
+        <v>3.55</v>
       </c>
       <c r="O4" t="n">
         <v>0.7</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>10.18</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>46010.38541666666</v>
+        <v>46010.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>682.25</v>
+        <v>710</v>
       </c>
       <c r="I5" t="n">
         <v>697.8278655524749</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K5" t="n">
-        <v>-4.86</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>6.57</v>
+        <v>10.35</v>
       </c>
       <c r="M5" t="n">
         <v>0.91</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>10.7</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>46027.38541666666</v>
+        <v>46027.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>713.3</v>
+        <v>685</v>
       </c>
       <c r="I6" t="n">
         <v>688.0416879814508</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>16.83333333333333</v>
+        <v>17</v>
       </c>
       <c r="K6" t="n">
-        <v>0.46</v>
+        <v>-3.52</v>
       </c>
       <c r="L6" t="n">
-        <v>4.45</v>
+        <v>4.65</v>
       </c>
       <c r="M6" t="n">
         <v>1.03</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>12.56</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>46055.55208333334</v>
+        <v>46056.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>610</v>
+        <v>672.55</v>
       </c>
       <c r="I7" t="n">
         <v>651.3612754771874</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>28</v>
+        <v>28.83333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>10.95</v>
+        <v>1.82</v>
       </c>
       <c r="L7" t="n">
         <v>4.55</v>
       </c>
       <c r="M7" t="n">
-        <v>1.65</v>
+        <v>7.21</v>
       </c>
       <c r="N7" t="n">
-        <v>3.72</v>
+        <v>11.42</v>
       </c>
       <c r="O7" t="n">
         <v>-7.65</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>13.53</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>46087.55208333334</v>
+        <v>46090.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>673.15</v>
+        <v>654.45</v>
       </c>
       <c r="I8" t="n">
         <v>671.2623405845447</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>34</v>
       </c>
       <c r="K8" t="n">
-        <v>0.09</v>
+        <v>-2.69</v>
       </c>
       <c r="L8" t="n">
         <v>6.93</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>11.09</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>46098.55208333334</v>
+        <v>46099.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>726</v>
+        <v>747.2</v>
       </c>
       <c r="I9" t="n">
         <v>726.9962811094711</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K9" t="n">
-        <v>-10.93</v>
+        <v>-14.17</v>
       </c>
       <c r="L9" t="n">
-        <v>11.49</v>
+        <v>18.54</v>
       </c>
       <c r="M9" t="n">
         <v>2.1</v>
       </c>
       <c r="N9" t="n">
-        <v>2.27</v>
+        <v>3.23</v>
       </c>
       <c r="O9" t="n">
         <v>1.24</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>9.289999999999999</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>46253.38541666666</v>
+        <v>46253.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>1452.7</v>
+        <v>1440</v>
       </c>
       <c r="I10" t="n">
         <v>1441.751570831326</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>154</v>
+        <v>154.1666666666667</v>
       </c>
       <c r="K10" t="n">
-        <v>94.42</v>
+        <v>92.72</v>
       </c>
       <c r="L10" t="n">
         <v>4.04</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>207</v>
+        <v>208</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>6</v>
+      </c>
+      <c r="U10" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>7.22</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>46261.55208333334</v>
+        <v>46262.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>1482</v>
+        <v>1605</v>
       </c>
       <c r="I11" t="n">
         <v>1530.741565198718</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.92</v>
+        <v>-11.46</v>
       </c>
       <c r="L11" t="n">
-        <v>5.07</v>
+        <v>12.22</v>
       </c>
       <c r="M11" t="n">
-        <v>0.38</v>
+        <v>2.81</v>
       </c>
       <c r="N11" t="n">
-        <v>2.56</v>
+        <v>9.18</v>
       </c>
       <c r="O11" t="n">
         <v>-1.73</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>9.630000000000001</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>46268.55208333334</v>
+        <v>46269.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>1639.1</v>
+        <v>1564.2</v>
       </c>
       <c r="I12" t="n">
         <v>1581.341340253469</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K12" t="n">
-        <v>2.12</v>
+        <v>-2.54</v>
       </c>
       <c r="L12" t="n">
         <v>5.07</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>12.1</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>46321.38541666666</v>
+        <v>46321.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>1414.7</v>
+        <v>1572.6</v>
       </c>
       <c r="I13" t="n">
         <v>1491.606209903476</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>52</v>
+        <v>52.16666666666666</v>
       </c>
       <c r="K13" t="n">
-        <v>9.56</v>
+        <v>-0.54</v>
       </c>
       <c r="L13" t="n">
         <v>6.99</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1242,6 +1409,12 @@
       <c r="Q14" t="n">
         <v>3</v>
       </c>
+      <c r="R14" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1984,7 +2157,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>43.6</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="6">
@@ -1994,7 +2167,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="7">
@@ -2004,7 +2177,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>175</v>
+        <v>175.2</v>
       </c>
     </row>
     <row r="8">
@@ -2014,7 +2187,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -2024,7 +2197,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36.4</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="10">
@@ -2034,7 +2207,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>143.8</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11">
@@ -2074,7 +2247,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17.99</v>
+        <v>12.87</v>
       </c>
     </row>
     <row r="15">
@@ -2084,7 +2257,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>36.55</v>
+        <v>32.46</v>
       </c>
     </row>
     <row r="16">
@@ -2094,7 +2267,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.58</v>
+        <v>-6.72</v>
       </c>
     </row>
     <row r="17">
@@ -2104,7 +2277,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>127.83</v>
+        <v>119.78</v>
       </c>
     </row>
     <row r="18">
@@ -2114,7 +2287,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>58.3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -2124,7 +2297,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.08</v>
+        <v>7.74</v>
       </c>
     </row>
     <row r="20">
@@ -2134,7 +2307,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.82</v>
+        <v>6.96</v>
       </c>
     </row>
     <row r="21">
@@ -2144,7 +2317,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11.49</v>
+        <v>18.54</v>
       </c>
     </row>
     <row r="22">
@@ -2164,7 +2337,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -2174,7 +2347,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.59</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="25">
@@ -2184,7 +2357,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.37</v>
+        <v>7.21</v>
       </c>
     </row>
     <row r="26">
@@ -2194,7 +2367,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.51</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="27">
@@ -2214,7 +2387,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
